--- a/report/DataAnalyze#250722.xlsx
+++ b/report/DataAnalyze#250722.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub_2\akshare\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D860CC6E-BE14-403E-B7CC-107ABC2FD82A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{621867F8-BEC0-461C-B6A9-5BD6687D2213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13096" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13096" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="食用盐" sheetId="1" r:id="rId1"/>
     <sheet name="土地出让费用" sheetId="2" r:id="rId2"/>
     <sheet name="家用车" sheetId="3" r:id="rId3"/>
+    <sheet name="水泥产量" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
   <si>
     <t>年份</t>
   </si>
@@ -55,6 +56,34 @@
   </si>
   <si>
     <t>自主品牌份额</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同比</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>平台期开端</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>疫情后投资拉动</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>近十年最低</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>累计值，需求疲软主导</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>产量（亿吨）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -95,7 +124,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -103,11 +132,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -117,6 +161,13 @@
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -778,4 +829,152 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4CABFB4-0A1B-45CB-93CB-93E6A78BAA11}">
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="7.53125" customWidth="1"/>
+    <col min="2" max="4" width="24" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A2" s="6">
+        <v>2015</v>
+      </c>
+      <c r="B2" s="6">
+        <v>23.59</v>
+      </c>
+      <c r="C2" s="6">
+        <v>-1.6E-2</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A3" s="6">
+        <v>2016</v>
+      </c>
+      <c r="B3" s="6">
+        <v>24.03</v>
+      </c>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A4" s="6">
+        <v>2017</v>
+      </c>
+      <c r="B4" s="6">
+        <v>23.16</v>
+      </c>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A5" s="6">
+        <v>2018</v>
+      </c>
+      <c r="B5" s="6">
+        <v>21.8</v>
+      </c>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A6" s="6">
+        <v>2019</v>
+      </c>
+      <c r="B6" s="6">
+        <v>23.3</v>
+      </c>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A7" s="6">
+        <v>2020</v>
+      </c>
+      <c r="B7" s="6">
+        <v>23.95</v>
+      </c>
+      <c r="C7" s="6">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A8" s="6">
+        <v>2021</v>
+      </c>
+      <c r="B8" s="6">
+        <v>23.63</v>
+      </c>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A9" s="6">
+        <v>2022</v>
+      </c>
+      <c r="B9" s="6">
+        <v>21.18</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-0.1</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A10" s="6">
+        <v>2023</v>
+      </c>
+      <c r="B10" s="6">
+        <v>20.23</v>
+      </c>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A11" s="6">
+        <v>2024</v>
+      </c>
+      <c r="B11" s="6">
+        <v>18.25</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-0.1</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C21" s="6"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>